--- a/tests/TC-04/results/teacher_timetables_even.xlsx
+++ b/tests/TC-04/results/teacher_timetables_even.xlsx
@@ -616,72 +616,90 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 113</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 113</t>
-        </is>
-      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>CS407 LEC
+(CSE_4_B)
+Room: 104</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>CS407 LEC
+(CSE_4_B)
+Room: 104</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 113</t>
+          <t>CS405 LEC
+(CSE_4_B)
+Room: 102</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 113</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t>CS405 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>CS405 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>CS405 LEC
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>DS151 LEC
-(CSE_4_B)
-Room: 103</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>DS151 LEC
-(CSE_4_B)
-Room: 103</t>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>CS404 TUT
+(CSE_4_B)
+Room: 108</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>CS151 TUT
-(CSE_4_B)
-Room: 106</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>CS151 TUT
-(CSE_4_B)
-Room: 106</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>CS406 LEC
+(CSE_4_B)
+Room: 107</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>CS406 LEC
+(CSE_4_B)
+Room: 107</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>CS406 LEC
+(CSE_4_B)
+Room: 107</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>CS411 TUT
+(CSE_4_B)
+Room: 108</t>
+        </is>
+      </c>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
@@ -693,88 +711,82 @@
       <c r="B4" s="6" t="inlineStr"/>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 106</t>
+          <t>CS403 LEC
+(CSE_4_B)
+Room: 119</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 106</t>
+          <t>CS403 LEC
+(CSE_4_B)
+Room: 119</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>DS151 LEC
-(CSE_4_B)
-Room: 103</t>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 104</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>DS151 LEC
-(CSE_4_B)
-Room: 103</t>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 104</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>DS151 LEC
-(CSE_4_B)
-Room: 103</t>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 104</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>DS151 LEC
-(CSE_4_B)
-Room: 103</t>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 104</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr"/>
       <c r="K4" s="6" t="inlineStr"/>
       <c r="L4" s="6" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
+      <c r="M4" s="6" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>CS402 LEC
 (CSE_4_B)
 Room: 108</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>CS402 LEC
 (CSE_4_B)
 Room: 108</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr"/>
       <c r="P4" s="4" t="inlineStr">
         <is>
-          <t>CS151 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>CS151 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>CS151 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 108</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr"/>
+      <c r="R4" s="6" t="inlineStr"/>
       <c r="S4" s="6" t="inlineStr"/>
-      <c r="T4" s="6" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>CS407 TUT
+(CSE_4_B)
+Room: 117</t>
+        </is>
+      </c>
       <c r="U4" s="6" t="inlineStr"/>
     </row>
     <row r="5" ht="35" customHeight="1">
@@ -786,88 +798,82 @@
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 108</t>
+          <t>CS404 LEC
+(CSE_4_B)
+Room: 111</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 108</t>
+          <t>CS404 LEC
+(CSE_4_B)
+Room: 111</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 106</t>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 104</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 106</t>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 104</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 106</t>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 104</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 106</t>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 104</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr"/>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>CS162 LEC
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>CS402 TUT
 (CSE_4_B)
 Room: 116</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>CS162 LEC
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>CS402 TUT
 (CSE_4_B)
 Room: 116</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 113</t>
-        </is>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 113</t>
-        </is>
-      </c>
-      <c r="R5" s="4" t="inlineStr">
-        <is>
-          <t>CS208 LEC
-(CSE_4_B)
-Room: 113</t>
-        </is>
-      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>CS402 TUT
+(CSE_4_B)
+Room: 116</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>CS409 TUT
+(CSE_4_B)
+Room: 106</t>
+        </is>
+      </c>
       <c r="U5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="35" customHeight="1">
@@ -877,84 +883,90 @@
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr"/>
-      <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>CS163 LEC
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>CS410 TUT
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>CS401 TUT
 (CSE_4_B)
 Room: 106</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>CS163 LEC
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>CS401 TUT
 (CSE_4_B)
 Room: 106</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 106</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>CS163 LEC
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>CS401 TUT
 (CSE_4_B)
 Room: 106</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="6" t="inlineStr"/>
-      <c r="K6" s="6" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>CS408 TUT
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>CS408 TUT
+(CSE_4_B)
+Room: 101</t>
+        </is>
+      </c>
       <c r="L6" s="6" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 108</t>
-        </is>
-      </c>
+      <c r="M6" s="6" t="inlineStr"/>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>CS165/CS201 LEC
-(CSE_4_B)
-Room: 108</t>
-        </is>
-      </c>
-      <c r="O6" s="6" t="inlineStr"/>
+          <t>CS403 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>CS403 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>CS162 LEC
-(CSE_4_B)
-Room: 116</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_4_B)
-Room: 116</t>
-        </is>
-      </c>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>CS162 LEC
-(CSE_4_B)
-Room: 116</t>
-        </is>
-      </c>
-      <c r="S6" s="6" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr">
-        <is>
-          <t>DS151 TUT
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
+          <t>CS403 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr"/>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>CS406 TUT
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>CS406 TUT
+(CSE_4_B)
+Room: 102</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr"/>
       <c r="U6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="35" customHeight="1">
@@ -966,43 +978,43 @@
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 106</t>
+          <t>CS404 LEC
+(CSE_4_B)
+Room: 111</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>CS163 LEC
-(CSE_4_B)
-Room: 106</t>
+          <t>CS404 LEC
+(CSE_4_B)
+Room: 111</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>CS165/CS201 LEC
+          <t>CS402 LEC
 (CSE_4_B)
 Room: 108</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>CS165/CS201 LEC
+          <t>CS402 LEC
 (CSE_4_B)
 Room: 108</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>CS165/CS201 LEC
+          <t>CS402 LEC
 (CSE_4_B)
 Room: 108</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>CS165/CS201 LEC
+          <t>CS402 LEC
 (CSE_4_B)
 Room: 108</t>
         </is>
@@ -1011,41 +1023,35 @@
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>CS162 TUT
-(CSE_4_B)
-Room: 104</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr"/>
-      <c r="P7" s="4" t="inlineStr">
-        <is>
-          <t>CS151 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>CS151 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="R7" s="4" t="inlineStr">
-        <is>
-          <t>CS151 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>CS403 TUT
+(CSE_4_B)
+Room: 104</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>CS403 TUT
+(CSE_4_B)
+Room: 104</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>CS403 TUT
+(CSE_4_B)
+Room: 104</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="5" t="inlineStr">
         <is>
-          <t>DA151 TUT
-(CSE_4_B)
-Room: 117</t>
+          <t>CS405 TUT
+(CSE_4_B)
+Room: 118</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr"/>

--- a/tests/TC-04/results/teacher_timetables_even.xlsx
+++ b/tests/TC-04/results/teacher_timetables_even.xlsx
@@ -618,86 +618,74 @@
       <c r="B3" s="3" t="inlineStr"/>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>CS407 LEC
-(CSE_4_B)
-Room: 104</t>
+          <t>CS403 LEC
+(CSE_4_B)
+Room: 113</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>CS407 LEC
-(CSE_4_B)
-Room: 104</t>
+          <t>CS403 LEC
+(CSE_4_B)
+Room: 113</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>CS405 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>CS405 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>CS405 LEC
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>CS405 LEC
-(CSE_4_B)
-Room: 102</t>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>CS402 TUT
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>CS402 TUT
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>CS402 TUT
+(CSE_4_B)
+Room: 119</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>CS404 TUT
-(CSE_4_B)
-Room: 108</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="4" t="inlineStr">
-        <is>
-          <t>CS406 LEC
-(CSE_4_B)
-Room: 107</t>
-        </is>
-      </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>CS406 LEC
-(CSE_4_B)
-Room: 107</t>
-        </is>
-      </c>
-      <c r="R3" s="4" t="inlineStr">
-        <is>
-          <t>CS406 LEC
-(CSE_4_B)
-Room: 107</t>
-        </is>
-      </c>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>CS401 TUT
+(CSE_4_B)
+Room: 114</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>CS401 TUT
+(CSE_4_B)
+Room: 114</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>CS401 TUT
+(CSE_4_B)
+Room: 114</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>CS411 TUT
-(CSE_4_B)
-Room: 108</t>
+          <t>CS404 TUT
+(CSE_4_B)
+Room: 119</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr"/>
@@ -711,45 +699,45 @@
       <c r="B4" s="6" t="inlineStr"/>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>CS403 LEC
-(CSE_4_B)
-Room: 119</t>
+          <t>CS406 LEC
+(CSE_4_B)
+Room: 110</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>CS403 LEC
-(CSE_4_B)
-Room: 119</t>
+          <t>CS406 LEC
+(CSE_4_B)
+Room: 110</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 104</t>
+          <t>CS405 LEC
+(CSE_4_B)
+Room: 119</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 104</t>
+          <t>CS405 LEC
+(CSE_4_B)
+Room: 119</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 104</t>
+          <t>CS405 LEC
+(CSE_4_B)
+Room: 119</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 104</t>
+          <t>CS405 LEC
+(CSE_4_B)
+Room: 119</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr"/>
@@ -760,21 +748,21 @@
         <is>
           <t>CS402 LEC
 (CSE_4_B)
-Room: 108</t>
+Room: 114</t>
         </is>
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
           <t>CS402 LEC
 (CSE_4_B)
-Room: 108</t>
+Room: 114</t>
         </is>
       </c>
       <c r="P4" s="4" t="inlineStr">
         <is>
           <t>CS402 LEC
 (CSE_4_B)
-Room: 108</t>
+Room: 114</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr"/>
@@ -782,9 +770,9 @@
       <c r="S4" s="6" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr">
         <is>
-          <t>CS407 TUT
-(CSE_4_B)
-Room: 117</t>
+          <t>CS408 TUT
+(CSE_4_B)
+Room: 107</t>
         </is>
       </c>
       <c r="U4" s="6" t="inlineStr"/>
@@ -796,82 +784,100 @@
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>CS404 LEC
-(CSE_4_B)
-Room: 111</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>CS404 LEC
-(CSE_4_B)
-Room: 111</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>CS407 TUT
+(CSE_4_B)
+Room: 106</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 114</t>
+        </is>
+      </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 104</t>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 114</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 104</t>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 114</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 104</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>CS401 LEC
-(CSE_4_B)
-Room: 104</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
+          <t>CS402 LEC
+(CSE_4_B)
+Room: 114</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>CS411 TUT
+(CSE_4_B)
+Room: 114</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>CS411 TUT
+(CSE_4_B)
+Room: 114</t>
+        </is>
+      </c>
       <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>CS402 TUT
-(CSE_4_B)
-Room: 116</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>CS402 TUT
-(CSE_4_B)
-Room: 116</t>
-        </is>
-      </c>
-      <c r="Q5" s="5" t="inlineStr">
-        <is>
-          <t>CS402 TUT
-(CSE_4_B)
-Room: 116</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>CS405 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>CS405 LEC
+(CSE_4_B)
+Room: 119</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>CS403 LEC
+(CSE_4_B)
+Room: 113</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>CS403 LEC
+(CSE_4_B)
+Room: 113</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>CS403 LEC
+(CSE_4_B)
+Room: 113</t>
+        </is>
+      </c>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="5" t="inlineStr">
         <is>
-          <t>CS409 TUT
-(CSE_4_B)
-Room: 106</t>
+          <t>CS410 TUT
+(CSE_4_B)
+Room: 105</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr"/>
@@ -883,87 +889,81 @@
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>CS410 TUT
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>CS401 TUT
-(CSE_4_B)
-Room: 106</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>CS401 TUT
-(CSE_4_B)
-Room: 106</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>CS401 TUT
-(CSE_4_B)
-Room: 106</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>CS408 TUT
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>CS408 TUT
-(CSE_4_B)
-Room: 101</t>
-        </is>
-      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>CS404 LEC
+(CSE_4_B)
+Room: 109</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>CS404 LEC
+(CSE_4_B)
+Room: 109</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>CS406 LEC
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>CS406 LEC
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>CS406 LEC
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>CS406 LEC
+(CSE_4_B)
+Room: 110</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr"/>
       <c r="L6" s="6" t="inlineStr"/>
       <c r="M6" s="6" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>CS403 LEC
-(CSE_4_B)
-Room: 119</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>CS403 LEC
-(CSE_4_B)
-Room: 119</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>CS403 LEC
-(CSE_4_B)
-Room: 119</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>CS406 TUT
-(CSE_4_B)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="inlineStr">
-        <is>
-          <t>CS406 TUT
-(CSE_4_B)
-Room: 102</t>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>CS405 TUT
+(CSE_4_B)
+Room: 106</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr"/>
+      <c r="P6" s="6" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 104</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 104</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 104</t>
         </is>
       </c>
       <c r="T6" s="6" t="inlineStr"/>
@@ -976,84 +976,90 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>CS404 LEC
-(CSE_4_B)
-Room: 111</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>CS404 LEC
-(CSE_4_B)
-Room: 111</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>CS406 TUT
+(CSE_4_B)
+Room: 109</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 104</t>
+        </is>
+      </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 108</t>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 104</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 108</t>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 104</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 108</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>CS402 LEC
-(CSE_4_B)
-Room: 108</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
+          <t>CS401 LEC
+(CSE_4_B)
+Room: 104</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>CS409 TUT
+(CSE_4_B)
+Room: 104</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>CS409 TUT
+(CSE_4_B)
+Room: 104</t>
+        </is>
+      </c>
       <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>CS403 TUT
 (CSE_4_B)
-Room: 104</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="inlineStr">
-        <is>
-          <t>CS403 TUT
-(CSE_4_B)
-Room: 104</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>CS403 TUT
-(CSE_4_B)
-Room: 104</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="5" t="inlineStr">
-        <is>
-          <t>CS405 TUT
-(CSE_4_B)
-Room: 118</t>
-        </is>
-      </c>
+Room: 113</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>CS404 LEC
+(CSE_4_B)
+Room: 109</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>CS404 LEC
+(CSE_4_B)
+Room: 109</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>CS404 LEC
+(CSE_4_B)
+Room: 109</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="inlineStr"/>
     </row>
   </sheetData>
